--- a/Ruby/watch-list-sell.xlsx
+++ b/Ruby/watch-list-sell.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,25 +505,25 @@
         <v>8.449999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="F2" t="n">
         <v>9.295</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.534759</v>
+        <v>0.543478</v>
       </c>
       <c r="H2" t="n">
-        <v>10.06</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>84500</v>
       </c>
       <c r="J2" t="n">
-        <v>93000</v>
+        <v>92500</v>
       </c>
       <c r="K2" t="n">
-        <v>8500.000000000015</v>
+        <v>8000.000000000007</v>
       </c>
     </row>
     <row r="3">
@@ -542,25 +542,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="F3" t="n">
         <v>10.78</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.970874</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.08</v>
+        <v>6.12</v>
       </c>
       <c r="I3" t="n">
         <v>24500</v>
       </c>
       <c r="J3" t="n">
-        <v>25500</v>
+        <v>26000</v>
       </c>
       <c r="K3" t="n">
-        <v>999.9999999999965</v>
+        <v>1499.999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -579,25 +579,25 @@
         <v>9.9</v>
       </c>
       <c r="E4" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="F4" t="n">
         <v>10.89</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.970874</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.03</v>
+        <v>5.05</v>
       </c>
       <c r="I4" t="n">
         <v>24750</v>
       </c>
       <c r="J4" t="n">
-        <v>25500</v>
+        <v>26000</v>
       </c>
       <c r="K4" t="n">
-        <v>749.9999999999974</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="5">
@@ -616,25 +616,62 @@
         <v>9.1</v>
       </c>
       <c r="E5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="F5" t="n">
         <v>10.01</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.534759</v>
+        <v>0.543478</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="I5" t="n">
         <v>45500</v>
       </c>
       <c r="J5" t="n">
-        <v>46500</v>
+        <v>46250</v>
       </c>
       <c r="K5" t="n">
-        <v>1000.000000000005</v>
+        <v>750.0000000000018</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PTT</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.626016</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>77500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>78125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
